--- a/data/raw/RPi_Pico_W_Official.xlsx
+++ b/data/raw/RPi_Pico_W_Official.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\szb75\Documents\Other_Proj\ArchitecturalCarbonModelingTool\ACT\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC9985C2-EA95-4101-B8EA-E4D1DDE0C426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F31162F-D9A2-4DB9-8C92-A6A2116C1894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{EFECAB25-8862-4039-872A-9D66B4D0B167}"/>
+    <workbookView xWindow="-120" yWindow="-18120" windowWidth="29040" windowHeight="17520" xr2:uid="{EFECAB25-8862-4039-872A-9D66B4D0B167}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/raw/RPi_Pico_W_Official.xlsx
+++ b/data/raw/RPi_Pico_W_Official.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\szb75\Documents\Other_Proj\ArchitecturalCarbonModelingTool\ACT\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21E5306E-0411-44E7-BB88-57795B06929E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AA101D3-E4BE-483E-B508-EA65BFF9DF01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{EFECAB25-8862-4039-872A-9D66B4D0B167}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AB$1035</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -166,7 +169,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="199">
   <si>
     <t>Quantity</t>
   </si>
@@ -439,9 +442,6 @@
   </si>
   <si>
     <t>LFB212G45CG7D227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active component(Signal Conditioning) </t>
   </si>
   <si>
     <t>2.4GHz Filter</t>
@@ -540,9 +540,6 @@
     <t>DMG1012T</t>
   </si>
   <si>
-    <t xml:space="preserve">Semiconductor Hardware </t>
-  </si>
-  <si>
     <t>Mosfet, N, SOT523, Vt=1V, Vgs=6V, Vds=20V, 450mA, 280mW</t>
   </si>
   <si>
@@ -826,6 +823,9 @@
   </si>
   <si>
     <t>Process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">active </t>
   </si>
 </sst>
 </file>
@@ -1489,7 +1489,7 @@
   <sheetData>
     <row r="1" spans="1:28" ht="48" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>0</v>
@@ -1498,10 +1498,10 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>2</v>
@@ -1525,16 +1525,16 @@
         <v>8</v>
       </c>
       <c r="M1" s="40" t="s">
+        <v>194</v>
+      </c>
+      <c r="N1" s="40" t="s">
+        <v>195</v>
+      </c>
+      <c r="O1" s="41" t="s">
         <v>196</v>
       </c>
-      <c r="N1" s="40" t="s">
+      <c r="P1" s="42" t="s">
         <v>197</v>
-      </c>
-      <c r="O1" s="41" t="s">
-        <v>198</v>
-      </c>
-      <c r="P1" s="42" t="s">
-        <v>199</v>
       </c>
       <c r="Q1" s="12"/>
       <c r="R1" s="13"/>
@@ -2129,10 +2129,10 @@
         <v>90</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E23" s="37" t="s">
-        <v>91</v>
+        <v>198</v>
       </c>
       <c r="F23" s="37"/>
       <c r="G23" s="19"/>
@@ -2140,24 +2140,24 @@
         <v>7.9945655212500003E-6</v>
       </c>
       <c r="I23" s="22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B24" s="14">
         <v>1</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="19"/>
@@ -2165,24 +2165,24 @@
         <v>7.1279205993187496E-4</v>
       </c>
       <c r="I24" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B25" s="14">
         <v>1</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E25" s="15" t="s">
         <v>100</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>101</v>
       </c>
       <c r="F25" s="15"/>
       <c r="G25" s="19"/>
@@ -2190,25 +2190,25 @@
         <v>2.8399999450924064E-4</v>
       </c>
       <c r="I25" s="22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T25" s="23"/>
     </row>
     <row r="26" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B26" s="14">
         <v>1</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="E26" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="19"/>
@@ -2219,7 +2219,7 @@
     </row>
     <row r="27" spans="1:24" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B27" s="14">
         <v>1</v>
@@ -2228,10 +2228,10 @@
         <v>47</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F27" s="15"/>
       <c r="G27" s="19"/>
@@ -2239,7 +2239,7 @@
         <v>3.2006611608124997E-5</v>
       </c>
       <c r="I27" s="22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="U27" s="13"/>
       <c r="V27" s="17"/>
@@ -2248,7 +2248,7 @@
     </row>
     <row r="28" spans="1:24" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B28" s="14">
         <v>1</v>
@@ -2257,56 +2257,56 @@
         <v>35</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F28" s="15"/>
       <c r="G28" s="19"/>
       <c r="H28" s="15"/>
       <c r="I28" s="16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:24" ht="29" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B29" s="14">
         <v>1</v>
       </c>
       <c r="C29" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>115</v>
-      </c>
       <c r="E29" s="15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F29" s="15"/>
       <c r="G29" s="19"/>
       <c r="H29" s="15"/>
       <c r="I29" s="16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B30" s="14">
         <v>1</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="E30" s="38" t="s">
-        <v>119</v>
+        <v>198</v>
       </c>
       <c r="F30" s="38"/>
       <c r="G30" s="19"/>
@@ -2314,24 +2314,24 @@
         <v>2.0128161418750003E-6</v>
       </c>
       <c r="I30" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:24" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B31" s="14">
         <v>4</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="E31" s="15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F31" s="15"/>
       <c r="G31" s="19"/>
@@ -2344,25 +2344,25 @@
     </row>
     <row r="32" spans="1:24" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B32" s="14">
         <v>3</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F32" s="15"/>
       <c r="G32" s="19"/>
       <c r="H32" s="26"/>
       <c r="I32" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="U32" s="13"/>
       <c r="V32" s="17"/>
@@ -2371,19 +2371,19 @@
     </row>
     <row r="33" spans="1:24" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B33" s="14">
         <v>1</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F33" s="15"/>
       <c r="G33" s="19"/>
@@ -2396,19 +2396,19 @@
     </row>
     <row r="34" spans="1:24" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B34" s="14">
         <v>1</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F34" s="15"/>
       <c r="H34" s="27"/>
@@ -2420,24 +2420,24 @@
     </row>
     <row r="35" spans="1:24" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B35" s="14">
         <v>1</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F35" s="15"/>
       <c r="H35" s="27"/>
       <c r="I35" s="16" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="U35" s="13"/>
       <c r="V35" s="17"/>
@@ -2446,24 +2446,24 @@
     </row>
     <row r="36" spans="1:24" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B36" s="14">
         <v>1</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F36" s="15"/>
       <c r="H36" s="25"/>
       <c r="I36" s="16" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="U36" s="13"/>
       <c r="V36" s="17"/>
@@ -2472,19 +2472,19 @@
     </row>
     <row r="37" spans="1:24" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B37" s="14">
         <v>2</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F37" s="15"/>
       <c r="H37" s="27"/>
@@ -2496,27 +2496,27 @@
     </row>
     <row r="38" spans="1:24" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B38" s="14">
         <v>2</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F38" s="15"/>
       <c r="H38" s="27"/>
       <c r="I38" s="16" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="U38" s="8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="V38" s="17">
         <f>0.001*0.01</f>
@@ -2533,27 +2533,27 @@
     </row>
     <row r="39" spans="1:24" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B39" s="14">
         <v>1</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F39" s="15"/>
       <c r="H39" s="15"/>
       <c r="I39" s="16" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="U39" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="V39" s="17">
         <f>0.001*0.04</f>
@@ -2570,27 +2570,27 @@
     </row>
     <row r="40" spans="1:24" ht="29" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B40" s="14">
         <v>1</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F40" s="15"/>
       <c r="H40" s="18"/>
       <c r="I40" s="16" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="U40" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="V40" s="17">
         <f>0.001*0.12</f>
@@ -2607,27 +2607,27 @@
     </row>
     <row r="41" spans="1:24" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B41" s="14">
         <v>1</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F41" s="15"/>
       <c r="H41" s="15"/>
       <c r="I41" s="16" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="U41" s="8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="V41" s="17">
         <f>0.001*0.6</f>
@@ -2644,41 +2644,41 @@
     </row>
     <row r="42" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B42" s="14">
         <v>1</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F42" s="15"/>
       <c r="H42" s="27"/>
       <c r="I42" s="16" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B43" s="14">
         <v>1</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F43" s="15"/>
       <c r="H43" s="27"/>
@@ -2686,19 +2686,19 @@
     </row>
     <row r="44" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B44" s="14">
         <v>1</v>
       </c>
       <c r="C44" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="E44" s="15" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F44" s="15"/>
       <c r="H44" s="28">
@@ -2708,64 +2708,64 @@
     </row>
     <row r="45" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B45" s="14">
         <v>1</v>
       </c>
       <c r="C45" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="E45" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F45" s="3"/>
       <c r="H45" s="15">
         <v>6.6899204670375001E-4</v>
       </c>
       <c r="I45" s="22" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="46" spans="1:24" ht="29" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B46" s="14">
         <v>6</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E46" s="37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F46" s="37"/>
       <c r="H46" s="19">
         <v>1.2232819228437503E-4</v>
       </c>
       <c r="I46" s="16" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="47" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B47" s="14">
         <v>1</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>11</v>
@@ -2774,21 +2774,21 @@
         <v>1.400466442375E-5</v>
       </c>
       <c r="I47" s="22" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="48" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B48" s="14">
         <v>1</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>11</v>
@@ -2797,7 +2797,7 @@
         <v>1.5076276397875E-4</v>
       </c>
       <c r="I48" s="22" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="49" spans="1:28" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2805,7 +2805,7 @@
     </row>
     <row r="50" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D50" s="15" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I50" s="19"/>
     </row>
@@ -6801,6 +6801,7 @@
       <c r="I1035" s="19"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AB1035" xr:uid="{8D642DB9-3E89-4895-A467-337B90A88803}"/>
   <hyperlinks>
     <hyperlink ref="L6" r:id="rId1" display="https://datasheets.raspberrypi.com/pico/pico-datasheet.pdf" xr:uid="{97A9FFA7-FD06-4705-AB98-4FC87EE50F73}"/>
     <hyperlink ref="I19" r:id="rId2" xr:uid="{2ABECDB6-D804-4528-AD87-771C69C14433}"/>
